--- a/result/Table202509.xlsx
+++ b/result/Table202509.xlsx
@@ -516,24 +516,24 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2025-10-14</t>
+          <t>2025-10-24</t>
         </is>
       </c>
       <c r="G2" t="inlineStr"/>
       <c r="H2" t="n">
-        <v>14</v>
+        <v>24</v>
       </c>
       <c r="I2" t="n">
         <v>100.96</v>
       </c>
       <c r="J2" t="n">
-        <v>104.66</v>
+        <v>130.79</v>
       </c>
       <c r="K2" t="n">
-        <v>3.66</v>
+        <v>29.55</v>
       </c>
       <c r="L2" t="n">
-        <v>3664.82</v>
+        <v>29546.35</v>
       </c>
     </row>
     <row r="3">
@@ -612,24 +612,24 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2025-10-10</t>
+          <t>2025-10-20</t>
         </is>
       </c>
       <c r="G4" t="inlineStr"/>
       <c r="H4" t="n">
-        <v>14</v>
+        <v>24</v>
       </c>
       <c r="I4" t="n">
         <v>12.49</v>
       </c>
       <c r="J4" t="n">
-        <v>13.12</v>
+        <v>12.47</v>
       </c>
       <c r="K4" t="n">
-        <v>5.04</v>
+        <v>-0.16</v>
       </c>
       <c r="L4" t="n">
-        <v>5044.04</v>
+        <v>-160.13</v>
       </c>
     </row>
     <row r="5">
@@ -908,24 +908,24 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2025-10-14</t>
+          <t>2025-10-16</t>
         </is>
       </c>
       <c r="G10" t="inlineStr"/>
       <c r="H10" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="I10" t="n">
         <v>42.8</v>
       </c>
       <c r="J10" t="n">
-        <v>42.17</v>
+        <v>39.78</v>
       </c>
       <c r="K10" t="n">
-        <v>-1.47</v>
+        <v>-7.06</v>
       </c>
       <c r="L10" t="n">
-        <v>-1471.96</v>
+        <v>-7056.07</v>
       </c>
     </row>
     <row r="11">
@@ -954,24 +954,24 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2025-09-26</t>
+          <t>2025-09-29</t>
         </is>
       </c>
       <c r="G11" t="inlineStr"/>
       <c r="H11" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="I11" t="n">
         <v>8.5</v>
       </c>
       <c r="J11" t="n">
-        <v>8.56</v>
+        <v>7.96</v>
       </c>
       <c r="K11" t="n">
-        <v>0.71</v>
+        <v>-6.35</v>
       </c>
       <c r="L11" t="n">
-        <v>705.88</v>
+        <v>-6352.94</v>
       </c>
     </row>
     <row r="12">
@@ -1050,24 +1050,24 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2025-09-23</t>
+          <t>2025-10-14</t>
         </is>
       </c>
       <c r="G13" t="inlineStr"/>
       <c r="H13" t="n">
-        <v>1</v>
+        <v>22</v>
       </c>
       <c r="I13" t="n">
         <v>15.82</v>
       </c>
       <c r="J13" t="n">
-        <v>14.87</v>
+        <v>14.48</v>
       </c>
       <c r="K13" t="n">
-        <v>-6.01</v>
+        <v>-8.470000000000001</v>
       </c>
       <c r="L13" t="n">
-        <v>-6005.06</v>
+        <v>-8470.290000000001</v>
       </c>
     </row>
     <row r="14">
@@ -1096,24 +1096,24 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2025-09-26</t>
+          <t>2025-10-20</t>
         </is>
       </c>
       <c r="G14" t="inlineStr"/>
       <c r="H14" t="n">
-        <v>4</v>
+        <v>28</v>
       </c>
       <c r="I14" t="n">
         <v>8.02</v>
       </c>
       <c r="J14" t="n">
-        <v>7.74</v>
+        <v>7.72</v>
       </c>
       <c r="K14" t="n">
-        <v>-3.49</v>
+        <v>-3.74</v>
       </c>
       <c r="L14" t="n">
-        <v>-3491.27</v>
+        <v>-3740.65</v>
       </c>
     </row>
     <row r="15">
@@ -1142,24 +1142,24 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2025-09-25</t>
+          <t>2025-09-26</t>
         </is>
       </c>
       <c r="G15" t="inlineStr"/>
       <c r="H15" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I15" t="n">
         <v>3.33</v>
       </c>
       <c r="J15" t="n">
-        <v>3.63</v>
+        <v>3.25</v>
       </c>
       <c r="K15" t="n">
-        <v>9.01</v>
+        <v>-2.4</v>
       </c>
       <c r="L15" t="n">
-        <v>9009.01</v>
+        <v>-2402.4</v>
       </c>
     </row>
     <row r="16">
@@ -1188,24 +1188,24 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2025-09-19</t>
+          <t>2025-10-10</t>
         </is>
       </c>
       <c r="G16" t="inlineStr"/>
       <c r="H16" t="n">
-        <v>1</v>
+        <v>22</v>
       </c>
       <c r="I16" t="n">
         <v>34.47</v>
       </c>
       <c r="J16" t="n">
-        <v>31.7</v>
+        <v>37.68</v>
       </c>
       <c r="K16" t="n">
-        <v>-8.039999999999999</v>
+        <v>9.31</v>
       </c>
       <c r="L16" t="n">
-        <v>-8035.97</v>
+        <v>9312.450000000001</v>
       </c>
     </row>
     <row r="17">
@@ -1284,24 +1284,24 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2025-09-16</t>
+          <t>2025-09-22</t>
         </is>
       </c>
       <c r="G18" t="inlineStr"/>
       <c r="H18" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="I18" t="n">
         <v>12.47</v>
       </c>
       <c r="J18" t="n">
-        <v>12.64</v>
+        <v>12.51</v>
       </c>
       <c r="K18" t="n">
-        <v>1.36</v>
+        <v>0.32</v>
       </c>
       <c r="L18" t="n">
-        <v>1363.27</v>
+        <v>320.77</v>
       </c>
     </row>
     <row r="19">
@@ -1380,24 +1380,24 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>2025-10-10</t>
+          <t>2025-10-13</t>
         </is>
       </c>
       <c r="G20" t="inlineStr"/>
       <c r="H20" t="n">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="I20" t="n">
         <v>48.76</v>
       </c>
       <c r="J20" t="n">
-        <v>47.02</v>
+        <v>44.99</v>
       </c>
       <c r="K20" t="n">
-        <v>-3.57</v>
+        <v>-7.73</v>
       </c>
       <c r="L20" t="n">
-        <v>-3568.5</v>
+        <v>-7731.75</v>
       </c>
     </row>
     <row r="21">
@@ -1526,24 +1526,24 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>2025-09-04</t>
+          <t>2025-09-19</t>
         </is>
       </c>
       <c r="G23" t="inlineStr"/>
       <c r="H23" t="n">
-        <v>2</v>
+        <v>17</v>
       </c>
       <c r="I23" t="n">
         <v>2.76</v>
       </c>
       <c r="J23" t="n">
-        <v>2.5</v>
+        <v>4.37</v>
       </c>
       <c r="K23" t="n">
-        <v>-9.42</v>
+        <v>58.33</v>
       </c>
       <c r="L23" t="n">
-        <v>-9420.290000000001</v>
+        <v>58333.33</v>
       </c>
     </row>
     <row r="24">
@@ -1764,24 +1764,24 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>2025-09-18</t>
+          <t>2025-09-22</t>
         </is>
       </c>
       <c r="G28" t="inlineStr"/>
       <c r="H28" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="I28" t="n">
         <v>6.66</v>
       </c>
       <c r="J28" t="n">
-        <v>7.15</v>
+        <v>6.82</v>
       </c>
       <c r="K28" t="n">
-        <v>7.36</v>
+        <v>2.4</v>
       </c>
       <c r="L28" t="n">
-        <v>7357.36</v>
+        <v>2402.4</v>
       </c>
     </row>
     <row r="29">
@@ -2052,24 +2052,24 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>2025-09-18</t>
+          <t>2025-09-23</t>
         </is>
       </c>
       <c r="G34" t="inlineStr"/>
       <c r="H34" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="I34" t="n">
         <v>17.66</v>
       </c>
       <c r="J34" t="n">
-        <v>19.36</v>
+        <v>19.09</v>
       </c>
       <c r="K34" t="n">
-        <v>9.630000000000001</v>
+        <v>8.1</v>
       </c>
       <c r="L34" t="n">
-        <v>9626.27</v>
+        <v>8097.4</v>
       </c>
     </row>
     <row r="35">
@@ -2198,24 +2198,24 @@
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>2025-09-10</t>
+          <t>2025-09-16</t>
         </is>
       </c>
       <c r="G37" t="inlineStr"/>
       <c r="H37" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="I37" t="n">
         <v>24.59</v>
       </c>
       <c r="J37" t="n">
-        <v>22.75</v>
+        <v>21.74</v>
       </c>
       <c r="K37" t="n">
-        <v>-7.48</v>
+        <v>-11.59</v>
       </c>
       <c r="L37" t="n">
-        <v>-7482.72</v>
+        <v>-11590.08</v>
       </c>
     </row>
     <row r="38">
@@ -2340,24 +2340,24 @@
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>2025-09-16</t>
+          <t>2025-10-10</t>
         </is>
       </c>
       <c r="G40" t="inlineStr"/>
       <c r="H40" t="n">
-        <v>8</v>
+        <v>32</v>
       </c>
       <c r="I40" t="n">
         <v>78.8</v>
       </c>
       <c r="J40" t="n">
-        <v>80.62</v>
+        <v>78.22</v>
       </c>
       <c r="K40" t="n">
-        <v>2.31</v>
+        <v>-0.74</v>
       </c>
       <c r="L40" t="n">
-        <v>2309.64</v>
+        <v>-736.04</v>
       </c>
     </row>
     <row r="41">
@@ -2486,24 +2486,24 @@
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>2025-09-16</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="G43" t="inlineStr"/>
       <c r="H43" t="n">
-        <v>8</v>
+        <v>74</v>
       </c>
       <c r="I43" t="n">
         <v>5.53</v>
       </c>
       <c r="J43" t="n">
-        <v>5.25</v>
+        <v>6.1</v>
       </c>
       <c r="K43" t="n">
-        <v>-5.06</v>
+        <v>10.31</v>
       </c>
       <c r="L43" t="n">
-        <v>-5063.29</v>
+        <v>10307.41</v>
       </c>
     </row>
     <row r="44">
@@ -2532,24 +2532,24 @@
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>2025-09-15</t>
+          <t>2025-10-17</t>
         </is>
       </c>
       <c r="G44" t="inlineStr"/>
       <c r="H44" t="n">
-        <v>10</v>
+        <v>42</v>
       </c>
       <c r="I44" t="n">
         <v>39.47</v>
       </c>
       <c r="J44" t="n">
-        <v>39.72</v>
+        <v>46.5</v>
       </c>
       <c r="K44" t="n">
-        <v>0.63</v>
+        <v>17.81</v>
       </c>
       <c r="L44" t="n">
-        <v>633.39</v>
+        <v>17811</v>
       </c>
     </row>
     <row r="45">
@@ -2628,24 +2628,24 @@
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>2025-09-26</t>
+          <t>2025-10-14</t>
         </is>
       </c>
       <c r="G46" t="inlineStr"/>
       <c r="H46" t="n">
-        <v>21</v>
+        <v>39</v>
       </c>
       <c r="I46" t="n">
         <v>52.91</v>
       </c>
       <c r="J46" t="n">
-        <v>61.44</v>
+        <v>63.8</v>
       </c>
       <c r="K46" t="n">
-        <v>16.12</v>
+        <v>20.58</v>
       </c>
       <c r="L46" t="n">
-        <v>16121.72</v>
+        <v>20582.12</v>
       </c>
     </row>
     <row r="47">
@@ -2724,24 +2724,24 @@
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>2025-09-10</t>
+          <t>2025-10-10</t>
         </is>
       </c>
       <c r="G48" t="inlineStr"/>
       <c r="H48" t="n">
-        <v>12</v>
+        <v>42</v>
       </c>
       <c r="I48" t="n">
         <v>57.28</v>
       </c>
       <c r="J48" t="n">
-        <v>70.31999999999999</v>
+        <v>80.55</v>
       </c>
       <c r="K48" t="n">
-        <v>22.77</v>
+        <v>40.62</v>
       </c>
       <c r="L48" t="n">
-        <v>22765.36</v>
+        <v>40625</v>
       </c>
     </row>
     <row r="49">
@@ -2770,24 +2770,24 @@
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>2025-09-10</t>
+          <t>2025-10-10</t>
         </is>
       </c>
       <c r="G49" t="inlineStr"/>
       <c r="H49" t="n">
-        <v>6</v>
+        <v>36</v>
       </c>
       <c r="I49" t="n">
         <v>31.35</v>
       </c>
       <c r="J49" t="n">
-        <v>31.65</v>
+        <v>36.63</v>
       </c>
       <c r="K49" t="n">
-        <v>0.96</v>
+        <v>16.84</v>
       </c>
       <c r="L49" t="n">
-        <v>956.9400000000001</v>
+        <v>16842.11</v>
       </c>
     </row>
     <row r="50">
@@ -2862,24 +2862,24 @@
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>2025-09-10</t>
+          <t>2025-09-19</t>
         </is>
       </c>
       <c r="G51" t="inlineStr"/>
       <c r="H51" t="n">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="I51" t="n">
         <v>34.21</v>
       </c>
       <c r="J51" t="n">
-        <v>32.12</v>
+        <v>30.52</v>
       </c>
       <c r="K51" t="n">
-        <v>-6.11</v>
+        <v>-10.79</v>
       </c>
       <c r="L51" t="n">
-        <v>-6109.32</v>
+        <v>-10786.32</v>
       </c>
     </row>
     <row r="52">
@@ -3208,24 +3208,24 @@
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>2025-09-05</t>
+          <t>2025-09-23</t>
         </is>
       </c>
       <c r="G58" t="inlineStr"/>
       <c r="H58" t="n">
-        <v>2</v>
+        <v>20</v>
       </c>
       <c r="I58" t="n">
         <v>2.9</v>
       </c>
       <c r="J58" t="n">
-        <v>2.75</v>
+        <v>2.72</v>
       </c>
       <c r="K58" t="n">
-        <v>-5.17</v>
+        <v>-6.21</v>
       </c>
       <c r="L58" t="n">
-        <v>-5172.41</v>
+        <v>-6206.9</v>
       </c>
     </row>
     <row r="59">
@@ -3304,24 +3304,24 @@
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>2025-09-04</t>
+          <t>2025-09-09</t>
         </is>
       </c>
       <c r="G60" t="inlineStr"/>
       <c r="H60" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="I60" t="n">
         <v>31.94</v>
       </c>
       <c r="J60" t="n">
-        <v>28.89</v>
+        <v>29.96</v>
       </c>
       <c r="K60" t="n">
-        <v>-9.550000000000001</v>
+        <v>-6.2</v>
       </c>
       <c r="L60" t="n">
-        <v>-9549.15</v>
+        <v>-6199.12</v>
       </c>
     </row>
     <row r="61">
@@ -3350,24 +3350,24 @@
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>2025-09-04</t>
+          <t>2025-09-18</t>
         </is>
       </c>
       <c r="G61" t="inlineStr"/>
       <c r="H61" t="n">
-        <v>2</v>
+        <v>16</v>
       </c>
       <c r="I61" t="n">
         <v>133.12</v>
       </c>
       <c r="J61" t="n">
-        <v>126.4</v>
+        <v>200.69</v>
       </c>
       <c r="K61" t="n">
-        <v>-5.05</v>
+        <v>50.76</v>
       </c>
       <c r="L61" t="n">
-        <v>-5048.08</v>
+        <v>50758.71</v>
       </c>
     </row>
     <row r="62">
@@ -3546,24 +3546,24 @@
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>2025-09-03</t>
+          <t>2025-09-04</t>
         </is>
       </c>
       <c r="G65" t="inlineStr"/>
       <c r="H65" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I65" t="n">
         <v>3.54</v>
       </c>
       <c r="J65" t="n">
-        <v>3.56</v>
+        <v>3.17</v>
       </c>
       <c r="K65" t="n">
-        <v>0.5600000000000001</v>
+        <v>-10.45</v>
       </c>
       <c r="L65" t="n">
-        <v>564.97</v>
+        <v>-10451.98</v>
       </c>
     </row>
     <row r="66">
@@ -3642,24 +3642,24 @@
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>2025-09-02</t>
+          <t>2025-09-03</t>
         </is>
       </c>
       <c r="G67" t="inlineStr"/>
       <c r="H67" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I67" t="n">
         <v>17.51</v>
       </c>
       <c r="J67" t="n">
-        <v>16.34</v>
+        <v>15.23</v>
       </c>
       <c r="K67" t="n">
-        <v>-6.68</v>
+        <v>-13.02</v>
       </c>
       <c r="L67" t="n">
-        <v>-6681.9</v>
+        <v>-13021.13</v>
       </c>
     </row>
     <row r="68">
